--- a/data/trans_camb/P23_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P23_R-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 0,98</t>
+          <t>-11,66; 1,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,13; -1,14</t>
+          <t>-13,49; -0,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 4,53</t>
+          <t>-8,13; 4,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,61; -3,22</t>
+          <t>-14,75; -2,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 1,24</t>
+          <t>-7,62; 1,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,54; -3,45</t>
+          <t>-12,72; -3,1</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 2,66</t>
+          <t>-26,06; 3,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,72; -3,06</t>
+          <t>-30,3; -0,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 13,57</t>
+          <t>-20,67; 14,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -9,77</t>
+          <t>-38,79; -7,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 3,38</t>
+          <t>-18,45; 2,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,93; -9,44</t>
+          <t>-30,97; -8,56</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 1,96</t>
+          <t>-9,22; 1,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,01; -2,76</t>
+          <t>-14,07; -3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 8,76</t>
+          <t>-2,14; 9,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 6,42</t>
+          <t>-4,86; 6,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,66</t>
+          <t>-4,45; 3,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,58; -0,54</t>
+          <t>-8,62; -0,67</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 3,61</t>
+          <t>-16,29; 2,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,64; -5,32</t>
+          <t>-24,65; -6,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 25,33</t>
+          <t>-5,9; 25,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 18,71</t>
+          <t>-12,08; 18,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 8,18</t>
+          <t>-9,31; 8,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,73; -1,26</t>
+          <t>-17,88; -1,47</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 0,08</t>
+          <t>-10,9; 0,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -7,32</t>
+          <t>-18,85; -7,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 2,87</t>
+          <t>-7,48; 2,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 1,52</t>
+          <t>-9,0; 1,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,33; -0,06</t>
+          <t>-7,55; 0,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -4,47</t>
+          <t>-12,07; -4,78</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 0,17</t>
+          <t>-19,49; 0,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,04; -14,58</t>
+          <t>-33,92; -15,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 7,78</t>
+          <t>-18,67; 7,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 4,6</t>
+          <t>-22,92; 3,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,89; -0,18</t>
+          <t>-16,14; 0,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,49; -10,51</t>
+          <t>-25,91; -10,8</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 7,06</t>
+          <t>-6,11; 6,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 3,92</t>
+          <t>-8,15; 3,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 17,08</t>
+          <t>4,92; 16,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 13,06</t>
+          <t>2,05; 13,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 9,79</t>
+          <t>1,39; 10,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 6,95</t>
+          <t>-1,42; 6,86</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 17,0</t>
+          <t>-12,45; 15,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 9,13</t>
+          <t>-16,87; 8,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,15; 67,77</t>
+          <t>15,86; 66,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,89; 52,3</t>
+          <t>6,54; 54,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 28,65</t>
+          <t>3,62; 29,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 19,94</t>
+          <t>-3,74; 19,87</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 10,05</t>
+          <t>-3,73; 9,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 4,18</t>
+          <t>-9,26; 4,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 8,18</t>
+          <t>-1,21; 8,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,1; 16,56</t>
+          <t>6,43; 16,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 7,84</t>
+          <t>-1,07; 7,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 8,93</t>
+          <t>0,01; 8,68</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 33,03</t>
+          <t>-10,9; 32,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 14,67</t>
+          <t>-25,21; 14,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 89,7</t>
+          <t>-8,7; 91,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43,28; 174,66</t>
+          <t>44,71; 180,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 41,37</t>
+          <t>-4,54; 38,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,99; 44,97</t>
+          <t>0,02; 43,13</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 4,84</t>
+          <t>-7,63; 5,8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,29</t>
+          <t>-7,19; 5,44</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,7</t>
+          <t>0,99; 6,78</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,77</t>
+          <t>2,84; 9,24</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,91</t>
+          <t>-2,24; 4,75</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 6,31</t>
+          <t>-0,31; 6,78</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-39,09; 32,27</t>
+          <t>-35,59; 38,76</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 35,59</t>
+          <t>-33,64; 36,12</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11,32; 731,73</t>
+          <t>12,92; 675,95</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>87,98; 1043,88</t>
+          <t>80,86; 880,14</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 63,0</t>
+          <t>-20,72; 61,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 78,58</t>
+          <t>-3,52; 87,57</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 6,05</t>
+          <t>-6,29; 5,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 3,9</t>
+          <t>-6,89; 4,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,49</t>
+          <t>-2,23; 1,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,67</t>
+          <t>-1,33; 2,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,6</t>
+          <t>-2,62; 2,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,41</t>
+          <t>-2,49; 2,28</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 77,3</t>
+          <t>-44,41; 76,47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-46,98; 52,34</t>
+          <t>-48,28; 54,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 578,47</t>
+          <t>-100,0; 352,49</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-75,79; 507,72</t>
+          <t>-74,15; 644,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 73,1</t>
+          <t>-41,78; 58,48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 68,24</t>
+          <t>-39,78; 65,12</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,21</t>
+          <t>-5,37; -0,41</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,55; -4,83</t>
+          <t>-9,69; -4,85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,18</t>
+          <t>-0,19; 4,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,69</t>
+          <t>-1,59; 2,75</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,26</t>
+          <t>-1,89; 1,26</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -1,78</t>
+          <t>-4,85; -1,62</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -0,51</t>
+          <t>-12,26; -0,99</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-21,85; -11,62</t>
+          <t>-22,03; -11,57</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 17,14</t>
+          <t>-0,77; 17,04</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 10,86</t>
+          <t>-5,86; 11,33</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,84</t>
+          <t>-5,48; 3,81</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-14,66; -5,37</t>
+          <t>-14,05; -4,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P23_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P23_R-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 1,45</t>
+          <t>-12,26; 0,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,49; -0,26</t>
+          <t>-13,16; -0,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 4,93</t>
+          <t>-7,23; 4,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,75; -2,46</t>
+          <t>-15,15; -3,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,05</t>
+          <t>-7,9; 1,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -3,1</t>
+          <t>-12,43; -3,67</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 3,75</t>
+          <t>-27,23; 1,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,3; -0,6</t>
+          <t>-29,44; -1,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 14,09</t>
+          <t>-19,23; 14,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,79; -7,76</t>
+          <t>-39,51; -9,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 2,85</t>
+          <t>-19,1; 3,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,97; -8,56</t>
+          <t>-30,45; -9,95</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 1,3</t>
+          <t>-8,82; 2,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,07; -3,12</t>
+          <t>-13,91; -2,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 9,09</t>
+          <t>-2,2; 8,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 6,47</t>
+          <t>-4,71; 6,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 3,69</t>
+          <t>-4,67; 3,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -0,67</t>
+          <t>-8,53; -0,4</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 2,58</t>
+          <t>-15,56; 3,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,65; -6,0</t>
+          <t>-24,7; -5,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 25,82</t>
+          <t>-5,42; 24,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 18,42</t>
+          <t>-11,95; 19,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 8,24</t>
+          <t>-9,48; 8,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,88; -1,47</t>
+          <t>-17,75; -1,03</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 0,05</t>
+          <t>-11,21; 0,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,85; -7,71</t>
+          <t>-18,75; -7,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 2,42</t>
+          <t>-7,61; 2,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 1,35</t>
+          <t>-8,86; 0,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 0,04</t>
+          <t>-7,91; 0,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,07; -4,78</t>
+          <t>-12,75; -4,68</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 0,11</t>
+          <t>-20,07; 0,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,92; -15,58</t>
+          <t>-33,2; -14,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 7,27</t>
+          <t>-19,03; 7,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 3,86</t>
+          <t>-22,29; 2,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 0,09</t>
+          <t>-16,8; 0,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,91; -10,8</t>
+          <t>-26,96; -11,29</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 6,44</t>
+          <t>-5,76; 6,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 3,76</t>
+          <t>-8,55; 4,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,92; 16,81</t>
+          <t>5,19; 16,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 13,13</t>
+          <t>2,26; 13,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 10,12</t>
+          <t>1,12; 9,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 6,86</t>
+          <t>-1,73; 6,74</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 15,74</t>
+          <t>-11,88; 16,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 8,82</t>
+          <t>-17,34; 9,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,86; 66,63</t>
+          <t>17,21; 66,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,54; 54,3</t>
+          <t>7,08; 53,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,62; 29,23</t>
+          <t>2,87; 28,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 19,87</t>
+          <t>-4,26; 19,78</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 9,51</t>
+          <t>-4,38; 9,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 4,36</t>
+          <t>-9,37; 3,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 8,44</t>
+          <t>-1,23; 8,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,43; 16,46</t>
+          <t>6,04; 16,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 7,49</t>
+          <t>-1,43; 7,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,01; 8,68</t>
+          <t>0,14; 8,88</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 32,24</t>
+          <t>-11,88; 31,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 14,68</t>
+          <t>-24,96; 12,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 91,73</t>
+          <t>-9,15; 91,92</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44,71; 180,08</t>
+          <t>43,04; 167,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 38,0</t>
+          <t>-6,0; 38,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,02; 43,13</t>
+          <t>0,54; 43,93</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 5,8</t>
+          <t>-7,55; 5,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 5,44</t>
+          <t>-7,23; 4,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,78</t>
+          <t>0,84; 6,62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,24</t>
+          <t>3,3; 9,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,75</t>
+          <t>-1,78; 4,64</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 6,78</t>
+          <t>-0,19; 7,05</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 38,76</t>
+          <t>-36,35; 34,25</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 36,12</t>
+          <t>-34,93; 31,38</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12,92; 675,95</t>
+          <t>18,04; 660,89</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>80,86; 880,14</t>
+          <t>98,45; 1066,5</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 61,63</t>
+          <t>-16,34; 59,59</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 87,57</t>
+          <t>-3,93; 86,14</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 5,81</t>
+          <t>-5,36; 5,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 4,01</t>
+          <t>-6,03; 4,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,26</t>
+          <t>-2,25; 1,47</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,7</t>
+          <t>-1,33; 2,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,23</t>
+          <t>-3,06; 2,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,28</t>
+          <t>-2,51; 2,33</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,41; 76,47</t>
+          <t>-41,57; 84,04</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-48,28; 54,29</t>
+          <t>-43,95; 63,07</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 352,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-74,15; 644,66</t>
+          <t>-64,61; 866,24</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 58,48</t>
+          <t>-47,45; 62,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-39,78; 65,12</t>
+          <t>-39,02; 68,26</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,37; -0,41</t>
+          <t>-5,41; -0,63</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -4,85</t>
+          <t>-9,64; -4,95</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,16</t>
+          <t>-0,55; 3,97</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,75</t>
+          <t>-1,48; 2,78</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,26</t>
+          <t>-2,02; 1,27</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,85; -1,62</t>
+          <t>-4,98; -1,66</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-12,26; -0,99</t>
+          <t>-12,23; -1,45</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -11,57</t>
+          <t>-22,01; -11,82</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 17,04</t>
+          <t>-1,97; 16,35</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 11,33</t>
+          <t>-5,61; 11,17</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 3,81</t>
+          <t>-5,87; 3,89</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -4,95</t>
+          <t>-14,51; -4,96</t>
         </is>
       </c>
     </row>
